--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N41_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N41_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.58731996091855</v>
+        <v>2.045439493649265</v>
       </c>
       <c r="D2" t="n">
-        <v>12.48808066353101</v>
+        <v>2.029313107823789</v>
       </c>
       <c r="E2" t="n">
-        <v>12.15126793033637</v>
+        <v>1.974581038679661</v>
       </c>
       <c r="F2" t="n">
-        <v>11.00795814839582</v>
+        <v>1.788793199114322</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.61665508385569</v>
+        <v>3.35020645112655</v>
       </c>
       <c r="D3" t="n">
-        <v>21.10979932556011</v>
+        <v>3.430342390403519</v>
       </c>
       <c r="E3" t="n">
-        <v>12.15126793033637</v>
+        <v>1.974581038679661</v>
       </c>
       <c r="F3" t="n">
-        <v>11.00795814839582</v>
+        <v>1.788793199114322</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>8.840893329287367</v>
+        <v>1.436645166009197</v>
       </c>
       <c r="D4" t="n">
-        <v>1.429175268263871</v>
+        <v>0.232240981092879</v>
       </c>
       <c r="E4" t="n">
-        <v>12.15126793033637</v>
+        <v>1.974581038679661</v>
       </c>
       <c r="F4" t="n">
-        <v>11.00795814839582</v>
+        <v>1.788793199114322</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.02758941972517</v>
+        <v>3.25448328070534</v>
       </c>
       <c r="D5" t="n">
-        <v>21.91443856421802</v>
+        <v>3.561096266685428</v>
       </c>
       <c r="E5" t="n">
-        <v>12.15126793033637</v>
+        <v>1.974581038679661</v>
       </c>
       <c r="F5" t="n">
-        <v>11.00795814839582</v>
+        <v>1.788793199114322</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>42.65811163379502</v>
+        <v>6.931943140491691</v>
       </c>
       <c r="D6" t="n">
-        <v>42.21533326492945</v>
+        <v>6.859991655551036</v>
       </c>
       <c r="E6" t="n">
-        <v>12.15126793033637</v>
+        <v>1.974581038679661</v>
       </c>
       <c r="F6" t="n">
-        <v>11.00795814839582</v>
+        <v>1.788793199114322</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>39.45086332212187</v>
+        <v>6.410765289844804</v>
       </c>
       <c r="D7" t="n">
-        <v>22.133063594372</v>
+        <v>3.59662283408545</v>
       </c>
       <c r="E7" t="n">
-        <v>12.15126793033637</v>
+        <v>1.974581038679661</v>
       </c>
       <c r="F7" t="n">
-        <v>11.00795814839582</v>
+        <v>1.788793199114322</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>40.79790059912136</v>
+        <v>6.629658847357221</v>
       </c>
       <c r="D8" t="n">
-        <v>40.80014052066459</v>
+        <v>6.630022834607996</v>
       </c>
       <c r="E8" t="n">
-        <v>12.15126793033637</v>
+        <v>1.974581038679661</v>
       </c>
       <c r="F8" t="n">
-        <v>11.00795814839582</v>
+        <v>1.788793199114322</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>27.58849272763464</v>
+        <v>4.483130068240629</v>
       </c>
       <c r="D9" t="n">
-        <v>11.12944167260878</v>
+        <v>1.808534271798927</v>
       </c>
       <c r="E9" t="n">
-        <v>12.15126793033637</v>
+        <v>1.974581038679661</v>
       </c>
       <c r="F9" t="n">
-        <v>11.00795814839582</v>
+        <v>1.788793199114322</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>41.54361886452084</v>
+        <v>6.750838065484637</v>
       </c>
       <c r="D10" t="n">
-        <v>20.60557953456521</v>
+        <v>3.348406674366847</v>
       </c>
       <c r="E10" t="n">
-        <v>12.15126793033637</v>
+        <v>1.974581038679661</v>
       </c>
       <c r="F10" t="n">
-        <v>11.00795814839582</v>
+        <v>1.788793199114322</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>27.96475838567536</v>
+        <v>4.544273237672246</v>
       </c>
       <c r="D11" t="n">
-        <v>16.37337301391282</v>
+        <v>2.660673114760833</v>
       </c>
       <c r="E11" t="n">
-        <v>12.15126793033637</v>
+        <v>1.974581038679661</v>
       </c>
       <c r="F11" t="n">
-        <v>11.00795814839582</v>
+        <v>1.788793199114322</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>34.75315392648565</v>
+        <v>5.647387513053919</v>
       </c>
       <c r="D12" t="n">
-        <v>18.2291973128488</v>
+        <v>2.96224456333793</v>
       </c>
       <c r="E12" t="n">
-        <v>12.15126793033637</v>
+        <v>1.974581038679661</v>
       </c>
       <c r="F12" t="n">
-        <v>11.00795814839582</v>
+        <v>1.788793199114322</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>10.19892835600846</v>
+        <v>1.657325857851374</v>
       </c>
       <c r="D13" t="n">
-        <v>15.20994357618026</v>
+        <v>2.471615831129292</v>
       </c>
       <c r="E13" t="n">
-        <v>12.15126793033637</v>
+        <v>1.974581038679661</v>
       </c>
       <c r="F13" t="n">
-        <v>11.00795814839582</v>
+        <v>1.788793199114322</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
